--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486760_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486760_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5595</v>
+        <v>4.1265</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2736</v>
+        <v>5.9151</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7141</v>
+        <v>-1.7886</v>
       </c>
       <c r="G2" t="n">
         <v>0.8864</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1433</v>
+        <v>-0.2897</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2201</v>
+        <v>-0.1384</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.07679999999999999</v>
+        <v>-0.1513</v>
       </c>
       <c r="V2" t="n">
         <v>2.1783</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3503</v>
+        <v>1.014</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2339</v>
+        <v>2.0962</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-1.0822</v>
       </c>
       <c r="G3" t="n">
         <v>-0.6389</v>
@@ -688,13 +688,13 @@
         <v>1.9308</v>
       </c>
       <c r="S3" t="n">
-        <v>0.502</v>
+        <v>-0.8343</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2131</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7111</v>
+        <v>-0.9097</v>
       </c>
       <c r="V3" t="n">
         <v>1.5218</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4243</v>
+        <v>0.5291</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0958</v>
+        <v>2.1509</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6715</v>
+        <v>-1.6218</v>
       </c>
       <c r="G4" t="n">
         <v>0.391</v>
@@ -766,13 +766,13 @@
         <v>2.3169</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3461</v>
+        <v>-1.2412</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5245</v>
+        <v>-0.4693</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.8216</v>
+        <v>-0.7719</v>
       </c>
       <c r="V4" t="n">
         <v>0.9932</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>S. SANCHEZ PARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1379</v>
+        <v>0.4074</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1379</v>
+        <v>2.4359</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-2.0285</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2.036</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.0558</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.9803</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>3.8717</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1.9185</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.9532</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>-1.8357</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-1.8628</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>0.0271</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1379</v>
+        <v>-0.586</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1379</v>
+        <v>-0.0762</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-0.5098</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. SANCHEZ PARRA</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0504</v>
+        <v>0.1379</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6568</v>
+        <v>0.1379</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6064</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.036</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0558</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9803</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8717</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9185</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9532</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.8357</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.8628</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0271</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5446</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9429999999999999</v>
+        <v>0.1379</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8554</v>
+        <v>0.1379</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0876</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RODRIGO HERNÁNDEZ</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4083</v>
+        <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6413</v>
+        <v>1.7009</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2329</v>
+        <v>-1.8909</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2551</v>
+        <v>-0.4605</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.393</v>
+        <v>0.3308</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1379</v>
+        <v>-0.7913</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6688</v>
+        <v>3.2859</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6688</v>
+        <v>2.4698</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.8161</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4137</v>
+        <v>-3.7464</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2758</v>
+        <v>-2.139</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1379</v>
+        <v>-1.6074</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>0.1931</v>
+        <v>2.51</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0607</v>
+        <v>-1.2826</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0275</v>
+        <v>-0.2487</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0882</v>
+        <v>-1.0339</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2856</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0.3794</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>J. RODRIGO HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.2304</v>
       </c>
       <c r="E8" t="n">
-        <v>2.294</v>
+        <v>-0.5377999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9074</v>
+        <v>0.3074</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3346</v>
+        <v>-0.2551</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1869</v>
+        <v>-0.393</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5214</v>
+        <v>0.1379</v>
       </c>
       <c r="J8" t="n">
-        <v>2.4876</v>
+        <v>-0.6688</v>
       </c>
       <c r="K8" t="n">
-        <v>1.2622</v>
+        <v>-0.6688</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2253</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.153</v>
+        <v>0.4137</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4491</v>
+        <v>0.2758</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2961</v>
+        <v>0.1379</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07190000000000001</v>
+        <v>0.1172</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7718</v>
+        <v>0.131</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8437</v>
+        <v>-0.0137</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4554</v>
+        <v>-0.2856</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4554</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0974</v>
+        <v>-0.5968</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8184</v>
+        <v>2.0872</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9158</v>
+        <v>-2.6839</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4605</v>
+        <v>1.3346</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3308</v>
+        <v>-0.1869</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7913</v>
+        <v>1.5214</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2859</v>
+        <v>2.4876</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4698</v>
+        <v>1.2622</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8161</v>
+        <v>1.2253</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.7464</v>
+        <v>-1.153</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.139</v>
+        <v>-1.4491</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6074</v>
+        <v>0.2961</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5446</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>2.51</v>
+        <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.19</v>
+        <v>-0.0552</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1313</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0587</v>
+        <v>-0.6202</v>
       </c>
       <c r="V9" t="n">
-        <v>0.008500000000000001</v>
+        <v>-2.4554</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3794</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.278</v>
+        <v>-1.2035</v>
       </c>
       <c r="E10" t="n">
         <v>-0.7865</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4915</v>
+        <v>-0.417</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8213</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9434</v>
+        <v>-0.8689</v>
       </c>
       <c r="T10" t="n">
         <v>-0.4415</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5019</v>
+        <v>-0.4274</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.8551</v>
+        <v>-1.6965</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8343</v>
+        <v>-0.6757</v>
       </c>
       <c r="F11" t="n">
         <v>-1.0208</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3034</v>
+        <v>-0.1448</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1655</v>
+        <v>-0.0069</v>
       </c>
       <c r="U11" t="n">
         <v>-0.1379</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.6514</v>
+        <v>-2.6804</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.6768</v>
+        <v>-2.7803</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0254</v>
+        <v>0.0999</v>
       </c>
       <c r="G12" t="n">
         <v>-2.912</v>
@@ -1390,13 +1390,13 @@
         <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4192</v>
+        <v>-0.4481</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2479</v>
+        <v>0.1445</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6671</v>
+        <v>-0.5926</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2856</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.256</v>
+        <v>-3.9787</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.0696</v>
+        <v>-3.9662</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1863</v>
+        <v>-0.0125</v>
       </c>
       <c r="G13" t="n">
         <v>-2.1461</v>
@@ -1468,13 +1468,13 @@
         <v>0.3862</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5737</v>
+        <v>-0.2965</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1932</v>
+        <v>-0.0898</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3805</v>
+        <v>-0.2067</v>
       </c>
       <c r="V13" t="n">
         <v>0.008500000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.637200000000002</v>
+        <v>-4.3614</v>
       </c>
       <c r="E14" t="n">
-        <v>7.5019</v>
+        <v>7.7776</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.1391</v>
+        <v>-12.1389</v>
       </c>
       <c r="G14" t="n">
         <v>-4.1376</v>
@@ -1525,7 +1525,7 @@
         <v>8.6274</v>
       </c>
       <c r="L14" t="n">
-        <v>3.210499999999999</v>
+        <v>3.210500000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-15.9758</v>
@@ -1546,16 +1546,16 @@
         <v>14.4808</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.0682</v>
+        <v>-5.7922</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6930999999999998</v>
+        <v>-0.4170000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-5.3751</v>
+        <v>-5.375100000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7415999999999998</v>
+        <v>0.7415999999999994</v>
       </c>
       <c r="W14" t="n">
         <v>6.0105</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7756</v>
+        <v>6.6263</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8373</v>
+        <v>5.5612</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9383</v>
+        <v>1.0651</v>
       </c>
       <c r="G15" t="n">
         <v>3.2179</v>
@@ -1624,13 +1624,13 @@
         <v>0.7723</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3147</v>
+        <v>1.1655</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0825</v>
+        <v>0.8064</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2322</v>
+        <v>0.359</v>
       </c>
       <c r="V15" t="n">
         <v>1.4707</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. GONZALEZ NOGALES</t>
+          <t>D. GUIJARRO GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2538</v>
+        <v>4.208</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8796</v>
+        <v>4.0354</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3742</v>
+        <v>0.1726</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.002</v>
+        <v>1.5278</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6415</v>
+        <v>-0.2897</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6435</v>
+        <v>1.8175</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7991</v>
+        <v>2.1292</v>
       </c>
       <c r="K16" t="n">
-        <v>2.0559</v>
+        <v>0.7457</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2569</v>
+        <v>1.3835</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8011</v>
+        <v>-0.6014</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4145</v>
+        <v>-1.0354</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3866</v>
+        <v>0.434</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3862</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2984</v>
+        <v>1.2481</v>
       </c>
       <c r="T16" t="n">
-        <v>3.4747</v>
+        <v>1.096</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1763</v>
+        <v>0.1521</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5712</v>
+        <v>2.7836</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5712</v>
+        <v>2.741</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. GUIJARRO GONZALEZ</t>
+          <t>J. GONZALEZ NOGALES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.019</v>
+        <v>2.8377</v>
       </c>
       <c r="E17" t="n">
-        <v>4.3457</v>
+        <v>1.9146</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3267</v>
+        <v>0.9231</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5278</v>
+        <v>-0.002</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2897</v>
+        <v>1.6415</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8175</v>
+        <v>-1.6435</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1292</v>
+        <v>0.7991</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7457</v>
+        <v>2.0559</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3835</v>
+        <v>-1.2569</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6014</v>
+        <v>-0.8011</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0354</v>
+        <v>-0.4145</v>
       </c>
       <c r="O17" t="n">
-        <v>0.434</v>
+        <v>-0.3866</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0591</v>
+        <v>1.8823</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4063</v>
+        <v>1.5097</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3472</v>
+        <v>0.3727</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7836</v>
+        <v>0.5712</v>
       </c>
       <c r="W17" t="n">
-        <v>2.741</v>
+        <v>0.5712</v>
       </c>
       <c r="X17" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7927</v>
+        <v>2.4354</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1192</v>
+        <v>1.8089</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6735</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>2.4149</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1847</v>
+        <v>1.8274</v>
       </c>
       <c r="T18" t="n">
-        <v>1.5166</v>
+        <v>1.2064</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6681</v>
+        <v>0.621</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2277</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3657</v>
+        <v>1.7808</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5472</v>
+        <v>2.6506</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1815</v>
+        <v>-0.8698</v>
       </c>
       <c r="G19" t="n">
         <v>1.9712</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6289</v>
+        <v>-0.2138</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0273</v>
+        <v>0.1307</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6562</v>
+        <v>-0.3445</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9421</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3476</v>
+        <v>0.3517</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3476</v>
+        <v>0.2483</v>
       </c>
       <c r="G20" t="n">
         <v>0.1379</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2097</v>
+        <v>0.2138</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2097</v>
+        <v>0.1104</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1455</v>
+        <v>0.1826</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0072</v>
+        <v>1.4209</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1527</v>
+        <v>-1.2383</v>
       </c>
       <c r="G21" t="n">
         <v>2.2062</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0924</v>
+        <v>1.4205</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2756</v>
+        <v>0.6892</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8169</v>
+        <v>0.7313</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5133</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8414</v>
+        <v>-1.494</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5552</v>
+        <v>-0.9347</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.2862</v>
+        <v>-0.5594</v>
       </c>
       <c r="G22" t="n">
         <v>-0.365</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2094</v>
+        <v>0.138</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5795</v>
+        <v>0.0411</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3701</v>
+        <v>0.0969</v>
       </c>
       <c r="V22" t="n">
         <v>0.8568</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.439</v>
+        <v>-1.9053</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6425</v>
+        <v>-1.3323</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7965</v>
+        <v>-0.573</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8156</v>
@@ -2248,13 +2248,13 @@
         <v>0.9654</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6234</v>
+        <v>-0.0897</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3587</v>
+        <v>-0.0485</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2647</v>
+        <v>-0.0412</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6894</v>
+        <v>-2.2261</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3128</v>
+        <v>0.7265</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.0022</v>
+        <v>-2.9526</v>
       </c>
       <c r="G24" t="n">
         <v>0.5738</v>
@@ -2326,13 +2326,13 @@
         <v>0.5792</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.2207</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5795</v>
+        <v>-0.1658</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1045</v>
+        <v>-0.0549</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2277</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.8017</v>
+        <v>-6.7809</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7123</v>
+        <v>-3.8157</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.0893</v>
+        <v>-2.9652</v>
       </c>
       <c r="G25" t="n">
         <v>-5.7295</v>
@@ -2404,13 +2404,13 @@
         <v>1.3515</v>
       </c>
       <c r="S25" t="n">
-        <v>0.055</v>
+        <v>0.0757</v>
       </c>
       <c r="T25" t="n">
-        <v>0.11</v>
+        <v>0.0066</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.055</v>
+        <v>0.0692</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5133</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>4.637399999999996</v>
+        <v>6.016199999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>12.139</v>
+        <v>12.1388</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.5015</v>
+        <v>-6.1227</v>
       </c>
       <c r="G26" t="n">
         <v>4.137600000000001</v>
@@ -2452,7 +2452,7 @@
         <v>4.8271</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.6894000000000005</v>
+        <v>-0.6893999999999996</v>
       </c>
       <c r="J26" t="n">
         <v>15.9758</v>
@@ -2482,13 +2482,13 @@
         <v>9.653699999999999</v>
       </c>
       <c r="S26" t="n">
-        <v>6.068299999999999</v>
+        <v>7.4471</v>
       </c>
       <c r="T26" t="n">
-        <v>5.3753</v>
+        <v>5.3752</v>
       </c>
       <c r="U26" t="n">
-        <v>0.6930999999999997</v>
+        <v>2.072</v>
       </c>
       <c r="V26" t="n">
         <v>-0.7418000000000005</v>
